--- a/testAutomation_v1.0/test/Manual/C1App/Admin_Gap_Analysis.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/Admin_Gap_Analysis.xlsx
@@ -571,7 +571,7 @@
     <t>Verify the maximum-grading-categories limit is enforced</t>
   </si>
   <si>
-    <t>Limit state; no counterpart. CAUTION: this case is BLOCKED, not passing - its precondition is a school already at its cap, and "3 July Test School 1" is shared, so holding it at the cap would break other suites mid-run. The modal copy is already verified word for word because the dialog is pre-rendered in the DOM. Counts as coverage designed, not coverage executed.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Limit state; no counterpart. CAUTION: this case is BLOCKED, not passing - its precondition is a school already at its cap, and "3 July Test School 1" is shared, so holding it at the cap would break other suites mid-run. The modal copy is already verified word for word because the dialog is pre-rendered in the DOM. Counts as coverage designed, not coverage executed.</t>
   </si>
   <si>
     <t>TST_GCAT_TC_5</t>
@@ -589,7 +589,7 @@
     <t>Verify the maximum-grading-scales limit is enforced</t>
   </si>
   <si>
-    <t>Limit state; no counterpart. CAUTION: BLOCKED for the same shared-school reason as TST_GCAT_TC_4, with its modal copy likewise already captured from the pre-rendered DOM.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Limit state; no counterpart. CAUTION: BLOCKED for the same shared-school reason as TST_GCAT_TC_4, with its modal copy likewise already captured from the pre-rendered DOM.</t>
   </si>
   <si>
     <t>TST_CMGT_TC_4</t>
@@ -598,7 +598,7 @@
     <t>Verify bulk-deleting multiple classes</t>
   </si>
   <si>
-    <t>Their delete cases (TC_CLS_023/024) are single-class only. Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Their delete cases (TC_CLS_023/024) are single-class only. Not Run.</t>
   </si>
   <si>
     <t>TST_CMGT_TC_6</t>
@@ -607,7 +607,7 @@
     <t>Verify bulk delete supports up to 50 classes</t>
   </si>
   <si>
-    <t>The 50-class cap is absent from their sheet. Edge case, Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The 50-class cap is absent from their sheet. Edge case, Not Run.</t>
   </si>
   <si>
     <t>TST_CLON_TC_3</t>
@@ -616,7 +616,7 @@
     <t>Verify components with no items are not selectable when copying</t>
   </si>
   <si>
-    <t>Clone edge case; their TC_CLS_029 covers only the happy path with a teacher and one material. Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Clone edge case; their TC_CLS_029 covers only the happy path with a teacher and one material. Not Run.</t>
   </si>
   <si>
     <t>TST_CTXC_TC_3</t>
@@ -625,7 +625,7 @@
     <t>Verify the context class appears/behaves correctly in the teacher login</t>
   </si>
   <si>
-    <t>Their TC_CLS_030 checks the admin login only. Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Their TC_CLS_030 checks the admin login only. Not Run.</t>
   </si>
   <si>
     <t>TST_CTXC_TC_4</t>
@@ -634,7 +634,7 @@
     <t>Verify the context class appears/behaves correctly in the student login</t>
   </si>
   <si>
-    <t>Their TC_CLS_030 checks the admin login only. Not Run. NOTE: the whole CTXC block (TC_1 to TC_4) is still at design stage - TC_2's expected result remains [ASSUMED].</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Their TC_CLS_030 checks the admin login only. Not Run. NOTE: the whole CTXC block (TC_1 to TC_4) is still at design stage - TC_2's expected result remains [ASSUMED].</t>
   </si>
   <si>
     <t>SUMMARY / METHOD</t>
@@ -1075,7 +1075,7 @@
     <t>Verify leaving the form with unsaved changes raises a confirmation</t>
   </si>
   <si>
-    <t>No counterpart. Not Run. Same class of behaviour as the Classes-tab Cancel-confirmation that a Phase 1 case originally got wrong.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No counterpart. Not Run. Same class of behaviour as the Classes-tab Cancel-confirmation that a Phase 1 case originally got wrong.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_20</t>
@@ -1084,7 +1084,7 @@
     <t>Verify selecting more than 50 students blocks the removal with a limit message</t>
   </si>
   <si>
-    <t>Documented 50-item cap; no counterpart. CAUTION: Blocked - needs a 50+ selection on the shared school.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Documented 50-item cap; no counterpart. CAUTION: Blocked - needs a 50+ selection on the shared school.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_21</t>
@@ -1102,7 +1102,7 @@
     <t>Verify the bulk-activation success dialog shows real text and not raw translation keys</t>
   </si>
   <si>
-    <t>A real defect we caught and pinned (screenshot bulk-activation-i18n-key.png in our folder). Nothing comparable in their sheet. Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). A real defect we caught and pinned (screenshot bulk-activation-i18n-key.png in our folder). Nothing comparable in their sheet. Not Run.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_10</t>
@@ -1111,7 +1111,7 @@
     <t>Verify the bulk-activation row checkbox exposes a real accessible label</t>
   </si>
   <si>
-    <t>Accessibility defect; their sheet has no a11y coverage at all in Students. Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Accessibility defect; their sheet has no a11y coverage at all in Students. Not Run.</t>
   </si>
   <si>
     <t>TST_SBLK_TC_12</t>
@@ -1120,7 +1120,7 @@
     <t>Verify a CSV that cannot be processed is rejected with a clear message</t>
   </si>
   <si>
-    <t>CSV-level failure path; their negatives are all row-level. Not Run.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). CSV-level failure path; their negatives are all row-level. Not Run.</t>
   </si>
   <si>
     <t>test/Manual/C1App/AdminApp-Students/AdminApp_Students_tab_test_cases.md + .xlsx - one consolidated register, 59 TCs across modules SLST (list/search/sort, 25), SPRF (profile, 22) and SBLK (bulk, 12).</t>
@@ -1279,7 +1279,7 @@
     <t>Verify the Staff tab loads with all expected components</t>
   </si>
   <si>
-    <t>No tab-load / component-inventory case in their Staff section.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No tab-load / component-inventory case in their Staff section.</t>
   </si>
   <si>
     <t>TST_STFL_TC_5</t>
@@ -1288,7 +1288,7 @@
     <t>Verify the list is unchanged when a term is typed but Search is not clicked</t>
   </si>
   <si>
-    <t>Search-trigger semantics; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Search-trigger semantics; no counterpart.</t>
   </si>
   <si>
     <t>TST_STFL_TC_7</t>
@@ -1297,7 +1297,7 @@
     <t>Verify the full staff list is restored when Clear is clicked</t>
   </si>
   <si>
-    <t>No counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No counterpart.</t>
   </si>
   <si>
     <t>TST_STFL_TC_10</t>
@@ -1306,7 +1306,7 @@
     <t>Verify a whitespace-only term enters the search banner state and returns everyone</t>
   </si>
   <si>
-    <t>Edge; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Edge; no counterpart.</t>
   </si>
   <si>
     <t>TST_STFL_TC_21</t>
@@ -1315,7 +1315,7 @@
     <t>Verify the list returns to the first page of 20 when the sort column changes after Load more</t>
   </si>
   <si>
-    <t>The interaction between sorting and pagination - a genuine defect surface their separate sort and Load-more cases cannot reach.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The interaction between sorting and pagination - a genuine defect surface their separate sort and Load-more cases cannot reach.</t>
   </si>
   <si>
     <t>TST_STFL_TC_26</t>
@@ -1324,7 +1324,7 @@
     <t>Verify the heading count matches the number of rows when the whole list is loaded</t>
   </si>
   <si>
-    <t>Count-vs-rows consistency; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Count-vs-rows consistency; no counterpart.</t>
   </si>
   <si>
     <t>TST_STFP_TC_3</t>
@@ -1339,7 +1339,7 @@
     <t>Verify an empty-state message is shown when the staff member belongs to no classes</t>
   </si>
   <si>
-    <t>Empty state on the profile; their TC_STF_008 assumes a class is always present.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Empty state on the profile; their TC_STF_008 assumes a class is always present.</t>
   </si>
   <si>
     <t>TST_STFP_TC_6</t>
@@ -1348,7 +1348,7 @@
     <t>Verify a user-visible error is shown and the page stays usable when the profile request fails</t>
   </si>
   <si>
-    <t>Failure path; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Failure path; no counterpart.</t>
   </si>
   <si>
     <t>TST_STFP_TC_8</t>
@@ -1357,7 +1357,7 @@
     <t>Verify each listed class shows its dates, join date and class key on a staff profile</t>
   </si>
   <si>
-    <t>Profile content depth; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Profile content depth; no counterpart.</t>
   </si>
   <si>
     <t>TST_STFP_TC_14</t>
@@ -1366,7 +1366,7 @@
     <t>Verify the administrator can reach Remove admin rights on their own staff profile</t>
   </si>
   <si>
-    <t>Self-service edge case - the neighbouring risk to their sole-admin negative, and nothing in their sheet covers it.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Self-service edge case - the neighbouring risk to their sole-admin negative, and nothing in their sheet covers it.</t>
   </si>
   <si>
     <t>TST_STFB_TC_5</t>
@@ -1375,7 +1375,7 @@
     <t>Verify the bulk row actions are unavailable when no rows are selected</t>
   </si>
   <si>
-    <t>Control gating; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Control gating; no counterpart.</t>
   </si>
   <si>
     <t>TST_STFB_TC_6</t>
@@ -1384,7 +1384,7 @@
     <t>Verify a previously saved draft is restored when the invitation form is re-opened</t>
   </si>
   <si>
-    <t>Auto-save/draft behaviour; no counterpart. Same auto-save mechanism as the Classes bulk form.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Auto-save/draft behaviour; no counterpart. Same auto-save mechanism as the Classes bulk form.</t>
   </si>
   <si>
     <t>TST_STFB_TC_7</t>
@@ -1399,7 +1399,7 @@
     <t>Verify per-field validation messages are shown when invitation rows are incomplete or invalid</t>
   </si>
   <si>
-    <t>Row-level validation for STAFF - note the mirror image of this is a GAP on the Students side, where their sheet has it and ours does not. Worth aligning the two registers.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Row-level validation for STAFF - note the mirror image of this is a GAP on the Students side, where their sheet has it and ours does not. Worth aligning the two registers.</t>
   </si>
   <si>
     <t>TST_STFB_TC_11</t>
@@ -1408,7 +1408,7 @@
     <t>Verify translated text is shown when the form upload error dialog is raised</t>
   </si>
   <si>
-    <t>Localisation defect case; their sheet has no i18n coverage outside the Generic Spanish case. CAUTION: Blocked.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Localisation defect case; their sheet has no i18n coverage outside the Generic Spanish case. CAUTION: Blocked.</t>
   </si>
   <si>
     <t>TST_STFB_TC_12</t>
@@ -1417,7 +1417,7 @@
     <t>Verify the browser tab title names the correct area when the form is opened from the Staff tab</t>
   </si>
   <si>
-    <t>Title/labelling defect; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Title/labelling defect; no counterpart.</t>
   </si>
   <si>
     <t>test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.md + .xlsx - one consolidated register, 56 TCs across modules STFL (list/search/sort, 26), STFP (profile + admin rights, 18) and STFB (bulk invite, 12).</t>
@@ -1480,7 +1480,7 @@
     <t>Verify the Library tab renders heading, count, search, sort and School licence section</t>
   </si>
   <si>
-    <t>No tab-load / component-inventory case in their Library section.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No tab-load / component-inventory case in their Library section.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_5</t>
@@ -1489,7 +1489,7 @@
     <t>Verify sorting compares titles case-insensitively rather than by code point</t>
   </si>
   <si>
-    <t>A precise characterisation of collation. NOTE the contrast with Students and Staff, where our cases assert code-point ordering - if Library really differs, that inconsistency is itself worth reporting to the product team.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). A precise characterisation of collation. NOTE the contrast with Students and Staff, where our cases assert code-point ordering - if Library really differs, that inconsistency is itself worth reporting to the product team.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_6</t>
@@ -1504,7 +1504,7 @@
     <t>Verify the sort control remains available and reorders results when a search is active</t>
   </si>
   <si>
-    <t>Sort-plus-search interaction; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Sort-plus-search interaction; no counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_8</t>
@@ -1549,7 +1549,7 @@
     <t>Verify the School licence section is not filtered when a search is applied</t>
   </si>
   <si>
-    <t>Cross-section interaction - the kind of leak a search feature commonly has. No counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Cross-section interaction - the kind of leak a search feature commonly has. No counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_18</t>
@@ -1564,7 +1564,7 @@
     <t>Verify a multi-word search term broadens the results by matching either word</t>
   </si>
   <si>
-    <t>OR-vs-AND semantics for search - the same class of question as the Classes filter gap, here answered on our side and absent on theirs.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). OR-vs-AND semantics for search - the same class of question as the Classes filter gap, here answered on our side and absent on theirs.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_21</t>
@@ -1573,7 +1573,7 @@
     <t>Verify close-match products are returned after the exact title matches</t>
   </si>
   <si>
-    <t>Result RANKING, not just membership; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Result RANKING, not just membership; no counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_22</t>
@@ -1585,7 +1585,7 @@
     <t>Verify an in-date school licence tile shows its expiry prefixed with "Expires"</t>
   </si>
   <si>
-    <t>Verbatim copy on the tile; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Verbatim copy on the tile; no counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_26</t>
@@ -1594,7 +1594,7 @@
     <t>Verify an expired school licence is still listed, marked "Expired" with a warning icon</t>
   </si>
   <si>
-    <t>The expired state; their TC_LIB_003 only considers a healthy licence.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The expired state; their TC_LIB_003 only considers a healthy licence.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_27</t>
@@ -1603,7 +1603,7 @@
     <t>Verify products held under a school licence also appear in the main product list</t>
   </si>
   <si>
-    <t>Consistency between the two sections; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Consistency between the two sections; no counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_28</t>
@@ -1612,7 +1612,7 @@
     <t>Verify a placeholder is rendered on a tile when the product has no cover image</t>
   </si>
   <si>
-    <t>Missing-asset edge; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Missing-asset edge; no counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_29</t>
@@ -1621,7 +1621,7 @@
     <t>Verify a very long product title wraps inside its tile without overflowing</t>
   </si>
   <si>
-    <t>Layout edge; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Layout edge; no counterpart.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_30</t>
@@ -1630,7 +1630,7 @@
     <t>Verify the School licence section is not rendered when the school holds no licence</t>
   </si>
   <si>
-    <t>The empty state - their case presupposes a licence exists.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The empty state - their case presupposes a licence exists.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_31</t>
@@ -1639,7 +1639,7 @@
     <t>Verify long product titles stay within the page width on a narrow screen</t>
   </si>
   <si>
-    <t>Responsive layout; their sheet has no responsive coverage anywhere.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Responsive layout; their sheet has no responsive coverage anywhere.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_4</t>
@@ -1648,7 +1648,7 @@
     <t>Verify the materials view shows Back, Add to a class and Activate materials controls</t>
   </si>
   <si>
-    <t>Component inventory for the umbrella view; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Component inventory for the umbrella view; no counterpart.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_5</t>
@@ -1657,7 +1657,7 @@
     <t>Verify a class-selection dialog listing the school classes opens on Add to a class</t>
   </si>
   <si>
-    <t>An entire action their sheet never exercises from the Library side.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). An entire action their sheet never exercises from the Library side.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_6</t>
@@ -1666,7 +1666,7 @@
     <t>Verify a component under an active school licence shows its status with start and expiry dates</t>
   </si>
   <si>
-    <t>Licence state at COMPONENT level; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Licence state at COMPONENT level; no counterpart.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_7</t>
@@ -1675,7 +1675,7 @@
     <t>Verify an unactivated component offers Activate and an expired one offers Re-activate</t>
   </si>
   <si>
-    <t>State-dependent control labels; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). State-dependent control labels; no counterpart.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_8</t>
@@ -1690,7 +1690,7 @@
     <t>Verify Back on the materials view returns the admin to the Library tab</t>
   </si>
   <si>
-    <t>No counterpart on the Library side (they check Back only from a student profile).</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No counterpart on the Library side (they check Back only from a student profile).</t>
   </si>
   <si>
     <t>test/Manual/C1App/AdminApp-Library/AdminApp_Library_tab_test_cases.md + .xlsx - one consolidated register, 41 TCs across modules LIBR (list/sort/search/school licence, 31) and UMBP (umbrella product materials view, 10).</t>
@@ -1870,7 +1870,7 @@
     <t>Verify the Reports tab loads with its empty state when the school has no reports</t>
   </si>
   <si>
-    <t>The empty state; their sheet starts from Create Report and never looks at the tab itself.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The empty state; their sheet starts from Create Report and never looks at the tab itself.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_3</t>
@@ -1879,7 +1879,7 @@
     <t>Verify the Reports tab is restored when "Go back" is used from class selection</t>
   </si>
   <si>
-    <t>A separate exit from Cancel; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). A separate exit from Cancel; no counterpart.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_17</t>
@@ -1888,7 +1888,7 @@
     <t>Verify the documented 1500-class selection limit is enforced</t>
   </si>
   <si>
-    <t>Documented cap; no counterpart. CAUTION: Blocked - needs 1500+ selectable classes.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Documented cap; no counterpart. CAUTION: Blocked - needs 1500+ selectable classes.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_29</t>
@@ -1897,7 +1897,7 @@
     <t>Verify the start date cannot be set earlier than the product floor of 1 January 2022</t>
   </si>
   <si>
-    <t>A real product boundary their date cases never touch.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). A real product boundary their date cases never touch.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_30</t>
@@ -1906,7 +1906,7 @@
     <t>Verify neither date can be set later than today</t>
   </si>
   <si>
-    <t>Future-date boundary; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Future-date boundary; no counterpart.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_32</t>
@@ -1915,7 +1915,7 @@
     <t>Verify a date cannot be entered by typing because the fields are read-only</t>
   </si>
   <si>
-    <t>Input-mechanism constraint - exactly the kind of detail that breaks automation when unrecorded.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Input-mechanism constraint - exactly the kind of detail that breaks automation when unrecorded.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_33</t>
@@ -1924,7 +1924,7 @@
     <t>Verify the custom date-range option is unavailable for report types that do not support it</t>
   </si>
   <si>
-    <t>Their TC_REP_013 lists the four types that DO support it but never checks the others are excluded.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Their TC_REP_013 lists the four types that DO support it but never checks the others are excluded.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_36</t>
@@ -1933,7 +1933,7 @@
     <t>Verify the custom grade-settings option is unavailable for the Estimated CEFR report</t>
   </si>
   <si>
-    <t>Negative counterpart to their TC_REP_014; no equivalent in their sheet.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Negative counterpart to their TC_REP_014; no equivalent in their sheet.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_38</t>
@@ -1942,7 +1942,7 @@
     <t>Verify the failure dialog is shown when report generation fails</t>
   </si>
   <si>
-    <t>Failure path; their sheet has no report-generation failure case. CAUTION: Blocked - needs an induced failure.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Failure path; their sheet has no report-generation failure case. CAUTION: Blocked - needs an induced failure.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_39</t>
@@ -1951,7 +1951,7 @@
     <t>Verify the partial-failure detail modal lists the excluded classes</t>
   </si>
   <si>
-    <t>Partial-failure path; no counterpart. CAUTION: Blocked. Note the symmetry with the Students bulk-activation partial-failure gap, where the roles are reversed.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Partial-failure path; no counterpart. CAUTION: Blocked. Note the symmetry with the Students bulk-activation partial-failure gap, where the roles are reversed.</t>
   </si>
   <si>
     <t>test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.md + .xlsx - one consolidated register, 39 TCs, module MRPT.</t>
@@ -2068,7 +2068,7 @@
     <t>Verify an over-long first name is handled correctly when no client-side limit exists</t>
   </si>
   <si>
-    <t>Boundary case on an UNCAPPED field - the absence of a maxlength is itself the finding. No counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Boundary case on an UNCAPPED field - the absence of a maxlength is itself the finding. No counterpart.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_6</t>
@@ -2077,7 +2077,7 @@
     <t>Verify an error is shown when the new password and its confirmation do not match</t>
   </si>
   <si>
-    <t>No counterpart; their My Profile case has no negative path at all.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No counterpart; their My Profile case has no negative path at all.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_7</t>
@@ -2092,7 +2092,7 @@
     <t>Verify the active profile tab is identifiable to assistive technology</t>
   </si>
   <si>
-    <t>Accessibility; no counterpart.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Accessibility; no counterpart.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_5</t>
@@ -2101,7 +2101,7 @@
     <t>Verify all five school tabs are shown with Classes active when a school is opened</t>
   </si>
   <si>
-    <t>The shell itself; their sheet assumes navigation works and never asserts it outside the multi-org case.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The shell itself; their sheet assumes navigation works and never asserts it outside the multi-org case.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_6</t>
@@ -2110,7 +2110,7 @@
     <t>Verify each tab loads its own page and becomes the active tab when selected</t>
   </si>
   <si>
-    <t>No counterpart in the Generic section.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). No counterpart in the Generic section.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_7</t>
@@ -2125,7 +2125,7 @@
     <t>Verify no dialog is visible when an admin screen first loads</t>
   </si>
   <si>
-    <t>A guard against stray pre-rendered dialogs becoming visible - directly informed by our finding that admin dialogs are pre-rendered in the DOM. No counterpart, and not a case another team would think to write.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). A guard against stray pre-rendered dialogs becoming visible - directly informed by our finding that admin dialogs are pre-rendered in the DOM. No counterpart, and not a case another team would think to write.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_9</t>
@@ -2134,7 +2134,7 @@
     <t>Verify the 50-item limit warnings use a consistent message pattern across screens</t>
   </si>
   <si>
-    <t>Cross-screen consistency; no counterpart. Ties together the 50-item caps in Students removal and Classes bulk delete.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Cross-screen consistency; no counterpart. Ties together the 50-item caps in Students removal and Classes bulk delete.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_10</t>
@@ -2143,7 +2143,7 @@
     <t>Verify destructive confirmations state their consequence before the action is taken</t>
   </si>
   <si>
-    <t>Cross-screen safety property; no counterpart. Their sheet asserts confirmation pop-ups exist per screen but never checks the wording is adequate.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). Cross-screen safety property; no counterpart. Their sheet asserts confirmation pop-ups exist per screen but never checks the wording is adequate.</t>
   </si>
   <si>
     <t>test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.md + .xlsx - one consolidated register, 37 TCs across modules ASHL (shell/header/nav), MYPR (my profile), INVI (notifications), FOOT (footer), SKEY (school key), SRQS (institution request), SADB (school dashboard) plus LIBR_TC_32. NOTE: the SADB multi-organisation cases are analysed on the MultiOrg sheet, not here.</t>
@@ -2197,7 +2197,7 @@
     <t>Verify every school the administrator manages is listed when My school accounts is opened</t>
   </si>
   <si>
-    <t>The entry point to multi-org itself; their three cases assume the admin has already arrived at a school.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The entry point to multi-org itself; their three cases assume the admin has already arrived at a school.</t>
   </si>
   <si>
     <t>TST_SADB_TC_4</t>
@@ -2206,7 +2206,7 @@
     <t>Verify two schools sharing a display name remain distinguishable by their school key</t>
   </si>
   <si>
-    <t>A genuine ambiguity risk in the org switcher; no counterpart. This is the case most likely to catch a real multi-org selection bug.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). A genuine ambiguity risk in the org switcher; no counterpart. This is the case most likely to catch a real multi-org selection bug.</t>
   </si>
   <si>
     <t>TST_SADB_TC_6</t>
@@ -2215,7 +2215,7 @@
     <t>Verify the teacher view lists the schools where the user teaches, not those they administer</t>
   </si>
   <si>
-    <t>The correctness of the teacher-view SCOPE. Their TC_ORG_003 only checks the toggle flips; ours checks it shows the right set of schools - the same negative-vs-positive-control point that recurs across this comparison.</t>
+    <t>REMOVED from our register 2026-09-21 (extra + not automated; archived copy kept). The correctness of the teacher-view SCOPE. Their TC_ORG_003 only checks the toggle flips; ours checks it shows the right set of schools - the same negative-vs-positive-control point that recurs across this comparison.</t>
   </si>
   <si>
     <t>NO DEDICATED REGISTER EXISTS. The nearest coverage is the SADB (school dashboard) module inside test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.md - 6 SADB cases, of which those analysed here are TC_2 to TC_7.</t>
@@ -2267,9 +2267,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor auto="1"/>
-      </patternFill>
+      <patternFill patternType="solid"/>
     </fill>
   </fills>
   <borders count="1">
@@ -3788,12 +3786,12 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>207</v>
       </c>
@@ -3801,7 +3799,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>209</v>
       </c>
@@ -3809,7 +3807,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>7</v>
       </c>
@@ -3817,7 +3815,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>131</v>
       </c>
@@ -3825,7 +3823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>153</v>
       </c>
@@ -3833,7 +3831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>211</v>
       </c>
@@ -3841,7 +3839,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>212</v>
       </c>
@@ -3852,7 +3850,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4769,12 +4767,12 @@
         <v>367</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>207</v>
       </c>
@@ -4782,7 +4780,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>209</v>
       </c>
@@ -4790,7 +4788,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>7</v>
       </c>
@@ -4798,7 +4796,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>131</v>
       </c>
@@ -4806,7 +4804,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>153</v>
       </c>
@@ -4814,7 +4812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>211</v>
       </c>
@@ -4822,7 +4820,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>212</v>
       </c>
@@ -4833,7 +4831,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5427,12 +5425,12 @@
         <v>466</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>207</v>
       </c>
@@ -5440,7 +5438,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>209</v>
       </c>
@@ -5448,7 +5446,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>7</v>
       </c>
@@ -5456,7 +5454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>131</v>
       </c>
@@ -5464,7 +5462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>153</v>
       </c>
@@ -5472,7 +5470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>211</v>
       </c>
@@ -5480,7 +5478,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>212</v>
       </c>
@@ -5491,7 +5489,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6085,12 +6083,12 @@
         <v>557</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>207</v>
       </c>
@@ -6098,7 +6096,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>209</v>
       </c>
@@ -6106,7 +6104,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>7</v>
       </c>
@@ -6114,7 +6112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>131</v>
       </c>
@@ -6122,7 +6120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>153</v>
       </c>
@@ -6130,7 +6128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>211</v>
       </c>
@@ -6138,7 +6136,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>212</v>
       </c>
@@ -6149,7 +6147,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6658,12 +6656,12 @@
         <v>644</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>207</v>
       </c>
@@ -6671,7 +6669,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>209</v>
       </c>
@@ -6679,7 +6677,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>7</v>
       </c>
@@ -6687,7 +6685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>131</v>
       </c>
@@ -6695,7 +6693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>153</v>
       </c>
@@ -6703,7 +6701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>211</v>
       </c>
@@ -6711,7 +6709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>212</v>
       </c>
@@ -6722,7 +6720,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7112,12 +7110,12 @@
         <v>708</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>207</v>
       </c>
@@ -7125,7 +7123,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>209</v>
       </c>
@@ -7133,7 +7131,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>7</v>
       </c>
@@ -7141,7 +7139,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>131</v>
       </c>
@@ -7149,7 +7147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>153</v>
       </c>
@@ -7157,7 +7155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>211</v>
       </c>
@@ -7165,7 +7163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>212</v>
       </c>
@@ -7176,7 +7174,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7328,12 +7326,12 @@
         <v>732</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>207</v>
       </c>
@@ -7341,7 +7339,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>209</v>
       </c>
@@ -7349,7 +7347,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>7</v>
       </c>
@@ -7357,7 +7355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>131</v>
       </c>
@@ -7365,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>153</v>
       </c>
@@ -7373,7 +7371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>211</v>
       </c>
@@ -7381,7 +7379,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>212</v>
       </c>
@@ -7392,6 +7390,6 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>